--- a/Shiny/Datos limpios/pricing_semanal_historico_sorgo.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico_sorgo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M566"/>
+  <dimension ref="A1:M570"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -24648,16 +24648,16 @@
         <v>45943</v>
       </c>
       <c r="D565">
-        <v>22180.73</v>
+        <v>21680.73</v>
       </c>
       <c r="E565">
         <v>0</v>
       </c>
       <c r="F565">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G565">
-        <v>21680.73</v>
+        <v>20680.73</v>
       </c>
       <c r="H565">
         <v>958.13</v>
@@ -24672,7 +24672,7 @@
         <v>958.13</v>
       </c>
       <c r="L565">
-        <v>22638.86</v>
+        <v>21638.86</v>
       </c>
       <c r="M565" t="inlineStr">
         <is>
@@ -24718,6 +24718,178 @@
         <v>7764.790000000001</v>
       </c>
       <c r="M566" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567">
+        <v>2025</v>
+      </c>
+      <c r="B567">
+        <v>44</v>
+      </c>
+      <c r="C567" s="2">
+        <v>45957</v>
+      </c>
+      <c r="D567">
+        <v>4707.66</v>
+      </c>
+      <c r="E567">
+        <v>59.86</v>
+      </c>
+      <c r="F567">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="G567">
+        <v>4766.74</v>
+      </c>
+      <c r="H567">
+        <v>8595.26</v>
+      </c>
+      <c r="I567">
+        <v>0</v>
+      </c>
+      <c r="J567">
+        <v>300</v>
+      </c>
+      <c r="K567">
+        <v>8295.26</v>
+      </c>
+      <c r="L567">
+        <v>13062</v>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568">
+        <v>2025</v>
+      </c>
+      <c r="B568">
+        <v>45</v>
+      </c>
+      <c r="C568" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D568">
+        <v>4676.16</v>
+      </c>
+      <c r="E568">
+        <v>511.44</v>
+      </c>
+      <c r="F568">
+        <v>30</v>
+      </c>
+      <c r="G568">
+        <v>5157.599999999999</v>
+      </c>
+      <c r="H568">
+        <v>8035.45</v>
+      </c>
+      <c r="I568">
+        <v>0</v>
+      </c>
+      <c r="J568">
+        <v>0</v>
+      </c>
+      <c r="K568">
+        <v>8035.45</v>
+      </c>
+      <c r="L568">
+        <v>13193.05</v>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569">
+        <v>2025</v>
+      </c>
+      <c r="B569">
+        <v>46</v>
+      </c>
+      <c r="C569" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D569">
+        <v>4929.81</v>
+      </c>
+      <c r="E569">
+        <v>106.67</v>
+      </c>
+      <c r="F569">
+        <v>0</v>
+      </c>
+      <c r="G569">
+        <v>5036.48</v>
+      </c>
+      <c r="H569">
+        <v>2704.3</v>
+      </c>
+      <c r="I569">
+        <v>0</v>
+      </c>
+      <c r="J569">
+        <v>0</v>
+      </c>
+      <c r="K569">
+        <v>2704.3</v>
+      </c>
+      <c r="L569">
+        <v>7740.780000000001</v>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570">
+        <v>2025</v>
+      </c>
+      <c r="B570">
+        <v>47</v>
+      </c>
+      <c r="C570" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D570">
+        <v>2590.8</v>
+      </c>
+      <c r="E570">
+        <v>120</v>
+      </c>
+      <c r="F570">
+        <v>0</v>
+      </c>
+      <c r="G570">
+        <v>2710.8</v>
+      </c>
+      <c r="H570">
+        <v>1003.34</v>
+      </c>
+      <c r="I570">
+        <v>0</v>
+      </c>
+      <c r="J570">
+        <v>0</v>
+      </c>
+      <c r="K570">
+        <v>1003.34</v>
+      </c>
+      <c r="L570">
+        <v>3714.14</v>
+      </c>
+      <c r="M570" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
